--- a/Smart Preset Assignment.xlsx
+++ b/Smart Preset Assignment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrew\srs-benchmark-rust\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06779613-BEDB-4631-899B-67B46D4AC015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B34D93-09DE-49DE-AC4F-5A93CDC2FFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="35">
   <si>
     <t>Experiment
 number</t>
@@ -102,6 +102,39 @@
     <t>mcs=20, ms=5</t>
   </si>
   <si>
+    <t>FSRS-7-short-secs-smart-kl</t>
+  </si>
+  <si>
+    <t>single</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>centroid</t>
+  </si>
+  <si>
+    <t>ward</t>
+  </si>
+  <si>
+    <t>FSRS-7-short-secs-smart-opt</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>optimal (Maha pre-merge)</t>
+  </si>
+  <si>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>optimal (KL pre-merge)</t>
+  </si>
+  <si>
     <t>1000 users</t>
   </si>
   <si>
@@ -160,8 +193,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -169,15 +205,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -494,43 +533,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="3"/>
@@ -542,28 +583,28 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -583,38 +624,38 @@
         <f>"-"</f>
         <v>-</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>0.32939499999999999</v>
       </c>
-      <c r="F3" s="5" t="str">
+      <c r="F3" s="7" t="str">
         <f>"-"</f>
         <v>-</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="7">
         <v>6.8756999999999999E-2</v>
       </c>
-      <c r="H3" s="5" t="str">
+      <c r="H3" s="7" t="str">
         <f>"-"</f>
         <v>-</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>0.348078</v>
       </c>
-      <c r="J3" s="5" t="str">
+      <c r="J3" s="7" t="str">
         <f>"-"</f>
         <v>-</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="7">
         <v>5.6654000000000003E-2</v>
       </c>
-      <c r="L3" s="5" t="str">
+      <c r="L3" s="7" t="str">
         <f>"-"</f>
         <v>-</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <f t="shared" ref="A4:A49" si="0">A3+1</f>
+        <f t="shared" ref="A4:A35" si="0">A3+1</f>
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -628,32 +669,32 @@
         <f t="shared" ref="D4:D9" si="1">"single"</f>
         <v>single</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>0.33519500000000002</v>
       </c>
-      <c r="F4" s="5">
-        <f t="shared" ref="F4:F49" si="2">IF(ISNUMBER(E4),(E4-E$3)/E$3,"")</f>
+      <c r="F4" s="7">
+        <f t="shared" ref="F4:F35" si="2">IF(ISNUMBER(E4),(E4-E$3)/E$3,"")</f>
         <v>1.7608038980555345E-2</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="7">
         <v>7.2276999999999994E-2</v>
       </c>
-      <c r="H4" s="5">
-        <f t="shared" ref="H4:H49" si="3">IF(ISNUMBER(G4),(G4-G$3)/G$3,"")</f>
+      <c r="H4" s="7">
+        <f t="shared" ref="H4:H35" si="3">IF(ISNUMBER(G4),(G4-G$3)/G$3,"")</f>
         <v>5.1194787439824245E-2</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>0.35338399999999998</v>
       </c>
-      <c r="J4" s="5">
-        <f t="shared" ref="J4:J49" si="4">IF(ISNUMBER(I4),(I4-I$3)/I$3,"")</f>
+      <c r="J4" s="7">
+        <f t="shared" ref="J4:J35" si="4">IF(ISNUMBER(I4),(I4-I$3)/I$3,"")</f>
         <v>1.524370974321841E-2</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="7">
         <v>5.9365000000000001E-2</v>
       </c>
-      <c r="L4" s="5">
-        <f t="shared" ref="L4:L49" si="5">IF(ISNUMBER(K4),(K4-K$3)/K$3,"")</f>
+      <c r="L4" s="7">
+        <f t="shared" ref="L4:L35" si="5">IF(ISNUMBER(K4),(K4-K$3)/K$3,"")</f>
         <v>4.7851872771560666E-2</v>
       </c>
     </row>
@@ -673,31 +714,31 @@
         <f t="shared" si="1"/>
         <v>single</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>0.33488400000000001</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="7">
         <f t="shared" si="2"/>
         <v>1.6663883786942793E-2</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="7">
         <v>7.1951000000000001E-2</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="7">
         <f t="shared" si="3"/>
         <v>4.6453452012158801E-2</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>0.35311399999999998</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="7">
         <f t="shared" si="4"/>
         <v>1.4468021535402942E-2</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="7">
         <v>5.9089000000000003E-2</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="7">
         <f t="shared" si="5"/>
         <v>4.2980195573128099E-2</v>
       </c>
@@ -718,31 +759,31 @@
         <f t="shared" si="1"/>
         <v>single</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>0.33346100000000001</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="7">
         <f t="shared" si="2"/>
         <v>1.234384249912723E-2</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="7">
         <v>7.0954000000000003E-2</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="7">
         <f t="shared" si="3"/>
         <v>3.1953110228776775E-2</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>0.35185300000000003</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="7">
         <f t="shared" si="4"/>
         <v>1.0845270312975908E-2</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="7">
         <v>5.8259999999999999E-2</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="7">
         <f t="shared" si="5"/>
         <v>2.8347512973488125E-2</v>
       </c>
@@ -763,31 +804,31 @@
         <f t="shared" si="1"/>
         <v>single</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>0.33048300000000003</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="7">
         <f t="shared" si="2"/>
         <v>3.3030252432490882E-3</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="7">
         <v>6.8983000000000003E-2</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="7">
         <f t="shared" si="3"/>
         <v>3.2869380572160506E-3</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>0.34951599999999999</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="7">
         <f t="shared" si="4"/>
         <v>4.131257936439519E-3</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="7">
         <v>5.6838E-2</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="7">
         <f t="shared" si="5"/>
         <v>3.2477847989550016E-3</v>
       </c>
@@ -808,31 +849,31 @@
         <f t="shared" si="1"/>
         <v>single</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>0.32973400000000003</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="7">
         <f t="shared" si="2"/>
         <v>1.0291595197256598E-3</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="7">
         <v>6.8513000000000004E-2</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="7">
         <f t="shared" si="3"/>
         <v>-3.5487295838968285E-3</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>0.34910400000000003</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="7">
         <f t="shared" si="4"/>
         <v>2.9476151896989378E-3</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="7">
         <v>5.6714000000000001E-2</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="7">
         <f t="shared" si="5"/>
         <v>1.059060260528781E-3</v>
       </c>
@@ -853,31 +894,31 @@
         <f t="shared" si="1"/>
         <v>single</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>0.32962900000000001</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="7">
         <f t="shared" si="2"/>
         <v>7.1039329680174857E-4</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="7">
         <v>6.8767999999999996E-2</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="7">
         <f t="shared" si="3"/>
         <v>1.5998371074940913E-4</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>0.34853600000000001</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="7">
         <f t="shared" si="4"/>
         <v>1.315797033998167E-3</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="7">
         <v>5.6838E-2</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="7">
         <f t="shared" si="5"/>
         <v>3.2477847989550016E-3</v>
       </c>
@@ -898,31 +939,31 @@
         <f t="shared" ref="D10:D15" si="6">"complete"</f>
         <v>complete</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>0.33498899999999998</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="7">
         <f t="shared" si="2"/>
         <v>1.6982650009866537E-2</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="7">
         <v>7.2566000000000005E-2</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="7">
         <f t="shared" si="3"/>
         <v>5.5397995840423618E-2</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>0.35314099999999998</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="7">
         <f t="shared" si="4"/>
         <v>1.4545590356184489E-2</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="7">
         <v>5.9561000000000003E-2</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="7">
         <f t="shared" si="5"/>
         <v>5.1311469622621522E-2</v>
       </c>
@@ -943,31 +984,31 @@
         <f t="shared" si="6"/>
         <v>complete</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>0.33506599999999997</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="7">
         <f t="shared" si="2"/>
         <v>1.7216411906677338E-2</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="7">
         <v>7.2447999999999999E-2</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="7">
         <f t="shared" si="3"/>
         <v>5.3681806943293046E-2</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>0.35323100000000002</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="7">
         <f t="shared" si="4"/>
         <v>1.4804153092123084E-2</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="7">
         <v>5.9499000000000003E-2</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="7">
         <f t="shared" si="5"/>
         <v>5.0217107353408411E-2</v>
       </c>
@@ -988,31 +1029,31 @@
         <f t="shared" si="6"/>
         <v>complete</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>0.335198</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="7">
         <f t="shared" si="2"/>
         <v>1.7617146586924523E-2</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="7">
         <v>7.2045999999999999E-2</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="7">
         <f t="shared" si="3"/>
         <v>4.783512951408584E-2</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>0.35344500000000001</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="7">
         <f t="shared" si="4"/>
         <v>1.5418957819799042E-2</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="7">
         <v>5.9265999999999999E-2</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="7">
         <f t="shared" si="5"/>
         <v>4.6104423341688072E-2</v>
       </c>
@@ -1033,31 +1074,31 @@
         <f t="shared" si="6"/>
         <v>complete</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>0.33399800000000002</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="7">
         <f t="shared" si="2"/>
         <v>1.3974104039223497E-2</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="7">
         <v>7.0849999999999996E-2</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="7">
         <f t="shared" si="3"/>
         <v>3.0440536963509138E-2</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>0.35263100000000003</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="7">
         <f t="shared" si="4"/>
         <v>1.3080401519199803E-2</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="7">
         <v>5.8424999999999998E-2</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13" s="7">
         <f t="shared" si="5"/>
         <v>3.1259928689942366E-2</v>
       </c>
@@ -1078,31 +1119,31 @@
         <f t="shared" si="6"/>
         <v>complete</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <v>0.33191100000000001</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="7">
         <f t="shared" si="2"/>
         <v>7.6382458750133371E-3</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="7">
         <v>6.9540000000000005E-2</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="7">
         <f t="shared" si="3"/>
         <v>1.1387931410620096E-2</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <v>0.35096699999999997</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="7">
         <f t="shared" si="4"/>
         <v>8.299863823625667E-3</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="7">
         <v>5.7456E-2</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="7">
         <f t="shared" si="5"/>
         <v>1.4156105482401898E-2</v>
       </c>
@@ -1123,31 +1164,31 @@
         <f t="shared" si="6"/>
         <v>complete</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="5">
         <v>0.3301</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="7">
         <f t="shared" si="2"/>
         <v>2.1402874967744235E-3</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="7">
         <v>6.8790000000000004E-2</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="7">
         <f t="shared" si="3"/>
         <v>4.7995113224842922E-4</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <v>0.34929300000000002</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="7">
         <f t="shared" si="4"/>
         <v>3.4905969351697653E-3</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="7">
         <v>5.6598999999999997E-2</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="7">
         <f t="shared" si="5"/>
         <v>-9.7080523881820223E-4</v>
       </c>
@@ -1168,31 +1209,31 @@
         <f t="shared" ref="D16:D21" si="7">"average"</f>
         <v>average</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="5">
         <v>0.335063</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="7">
         <f t="shared" si="2"/>
         <v>1.720730430030816E-2</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="7">
         <v>7.2500999999999996E-2</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="7">
         <f t="shared" si="3"/>
         <v>5.4452637549631269E-2</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <v>0.35321200000000003</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="7">
         <f t="shared" si="4"/>
         <v>1.4749567625647204E-2</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16" s="7">
         <v>5.9518000000000001E-2</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16" s="7">
         <f t="shared" si="5"/>
         <v>5.0552476435909176E-2</v>
       </c>
@@ -1213,31 +1254,31 @@
         <f t="shared" si="7"/>
         <v>average</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="5">
         <v>0.33519900000000002</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="7">
         <f t="shared" si="2"/>
         <v>1.762018245571436E-2</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="7">
         <v>7.2346999999999995E-2</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="7">
         <f t="shared" si="3"/>
         <v>5.2212865599138937E-2</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <v>0.353379</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="7">
         <f t="shared" si="4"/>
         <v>1.5229345146777446E-2</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17" s="7">
         <v>5.9459999999999999E-2</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L17" s="7">
         <f t="shared" si="5"/>
         <v>4.9528718184064603E-2</v>
       </c>
@@ -1258,31 +1299,31 @@
         <f t="shared" si="7"/>
         <v>average</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="5">
         <v>0.335038</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="7">
         <f t="shared" si="2"/>
         <v>1.7131407580564396E-2</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="7">
         <v>7.1758000000000002E-2</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="7">
         <f t="shared" si="3"/>
         <v>4.3646465087191173E-2</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="5">
         <v>0.353348</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="7">
         <f t="shared" si="4"/>
         <v>1.5140284648843066E-2</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="7">
         <v>5.9088000000000002E-2</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18" s="7">
         <f t="shared" si="5"/>
         <v>4.296254456878594E-2</v>
       </c>
@@ -1303,31 +1344,31 @@
         <f t="shared" si="7"/>
         <v>average</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="5">
         <v>0.33240799999999998</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="7">
         <f t="shared" si="2"/>
         <v>9.1470726635194469E-3</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="7">
         <v>7.0014000000000007E-2</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="7">
         <f t="shared" si="3"/>
         <v>1.8281774946551015E-2</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="5">
         <v>0.35127999999999998</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="7">
         <f t="shared" si="4"/>
         <v>9.1990875608340163E-3</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="7">
         <v>5.7771999999999997E-2</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="7">
         <f t="shared" si="5"/>
         <v>1.9733822854520314E-2</v>
       </c>
@@ -1348,31 +1389,31 @@
         <f t="shared" si="7"/>
         <v>average</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <v>0.33015099999999997</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="7">
         <f t="shared" si="2"/>
         <v>2.2951168050516215E-3</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="7">
         <v>6.8742999999999999E-2</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="7">
         <f t="shared" si="3"/>
         <v>-2.0361563186293939E-4</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="5">
         <v>0.34943400000000002</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="7">
         <f t="shared" si="4"/>
         <v>3.8956785548067497E-3</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="7">
         <v>5.6834999999999997E-2</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L20" s="7">
         <f t="shared" si="5"/>
         <v>3.1948317859285076E-3</v>
       </c>
@@ -1393,31 +1434,31 @@
         <f t="shared" si="7"/>
         <v>average</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="5">
         <v>0.32971800000000001</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="7">
         <f t="shared" si="2"/>
         <v>9.8058561908959683E-4</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="7">
         <v>6.8766999999999995E-2</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="7">
         <f t="shared" si="3"/>
         <v>1.4543973704489905E-4</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="5">
         <v>0.34888200000000003</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="7">
         <f t="shared" si="4"/>
         <v>2.3098271077173133E-3</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="7">
         <v>5.6702000000000002E-2</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L21" s="7">
         <f t="shared" si="5"/>
         <v>8.4724820842304921E-4</v>
       </c>
@@ -1438,31 +1479,31 @@
         <f t="shared" ref="D22:D27" si="8">"centroid"</f>
         <v>centroid</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="5">
         <v>0.33516299999999999</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="7">
         <f t="shared" si="2"/>
         <v>1.7510891179283217E-2</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="7">
         <v>7.2423000000000001E-2</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="7">
         <f t="shared" si="3"/>
         <v>5.3318207600680699E-2</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="5">
         <v>0.353323</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="7">
         <f t="shared" si="4"/>
         <v>1.5068461666637936E-2</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22" s="7">
         <v>5.9503E-2</v>
       </c>
-      <c r="L22" s="5">
+      <c r="L22" s="7">
         <f t="shared" si="5"/>
         <v>5.028771137077695E-2</v>
       </c>
@@ -1483,31 +1524,31 @@
         <f t="shared" si="8"/>
         <v>centroid</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="5">
         <v>0.33517400000000003</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="7">
         <f t="shared" si="2"/>
         <v>1.7544285735970597E-2</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="7">
         <v>7.2163000000000005E-2</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="7">
         <f t="shared" si="3"/>
         <v>4.9536774437511907E-2</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="5">
         <v>0.35335899999999998</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J23" s="7">
         <f t="shared" si="4"/>
         <v>1.5171886761013279E-2</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="7">
         <v>5.9355999999999999E-2</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L23" s="7">
         <f t="shared" si="5"/>
         <v>4.7693013732481304E-2</v>
       </c>
@@ -1528,31 +1569,31 @@
         <f t="shared" si="8"/>
         <v>centroid</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="5">
         <v>0.33401900000000001</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="7">
         <f t="shared" si="2"/>
         <v>1.4037857283808245E-2</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="7">
         <v>7.1063000000000001E-2</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="7">
         <f t="shared" si="3"/>
         <v>3.3538403362566756E-2</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="5">
         <v>0.35237800000000002</v>
       </c>
-      <c r="J24" s="5">
+      <c r="J24" s="7">
         <f t="shared" si="4"/>
         <v>1.2353552939283799E-2</v>
       </c>
-      <c r="K24" s="5">
+      <c r="K24" s="7">
         <v>5.8376999999999998E-2</v>
       </c>
-      <c r="L24" s="5">
+      <c r="L24" s="7">
         <f t="shared" si="5"/>
         <v>3.0412680481519315E-2</v>
       </c>
@@ -1573,31 +1614,31 @@
         <f t="shared" si="8"/>
         <v>centroid</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="5">
         <v>0.331451</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="7">
         <f t="shared" si="2"/>
         <v>6.2417462317278715E-3</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="7">
         <v>6.9528999999999994E-2</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="7">
         <f t="shared" si="3"/>
         <v>1.1227947699870485E-2</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="5">
         <v>0.35039599999999999</v>
       </c>
-      <c r="J25" s="5">
+      <c r="J25" s="7">
         <f t="shared" si="4"/>
         <v>6.6594269100603504E-3</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K25" s="7">
         <v>5.7417999999999997E-2</v>
       </c>
-      <c r="L25" s="5">
+      <c r="L25" s="7">
         <f t="shared" si="5"/>
         <v>1.348536731740025E-2</v>
       </c>
@@ -1618,31 +1659,31 @@
         <f t="shared" si="8"/>
         <v>centroid</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="5">
         <v>0.32999099999999998</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="7">
         <f t="shared" si="2"/>
         <v>1.8093777986914964E-3</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="7">
         <v>6.8636000000000003E-2</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="7">
         <f t="shared" si="3"/>
         <v>-1.7598208182439041E-3</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="5">
         <v>0.34928900000000002</v>
       </c>
-      <c r="J26" s="5">
+      <c r="J26" s="7">
         <f t="shared" si="4"/>
         <v>3.4791052580169317E-3</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="7">
         <v>5.6739999999999999E-2</v>
       </c>
-      <c r="L26" s="5">
+      <c r="L26" s="7">
         <f t="shared" si="5"/>
         <v>1.5179863734245736E-3</v>
       </c>
@@ -1663,31 +1704,31 @@
         <f t="shared" si="8"/>
         <v>centroid</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="5">
         <v>0.32963599999999998</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="7">
         <f t="shared" si="2"/>
         <v>7.3164437832994196E-4</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="7">
         <v>6.8752999999999995E-2</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="7">
         <f t="shared" si="3"/>
         <v>-5.8175894818040355E-5</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="5">
         <v>0.348659</v>
       </c>
-      <c r="J27" s="5">
+      <c r="J27" s="7">
         <f t="shared" si="4"/>
         <v>1.6691661064474003E-3</v>
       </c>
-      <c r="K27" s="5">
+      <c r="K27" s="7">
         <v>5.6681000000000002E-2</v>
       </c>
-      <c r="L27" s="5">
+      <c r="L27" s="7">
         <f t="shared" si="5"/>
         <v>4.7657711723795752E-4</v>
       </c>
@@ -1708,31 +1749,31 @@
         <f t="shared" ref="D28:D33" si="9">"ward"</f>
         <v>ward</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="5">
         <v>0.33490999999999999</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="7">
         <f t="shared" si="2"/>
         <v>1.6742816375476227E-2</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="7">
         <v>7.2561E-2</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="7">
         <f t="shared" si="3"/>
         <v>5.5325275971901074E-2</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="5">
         <v>0.35309400000000002</v>
       </c>
-      <c r="J28" s="5">
+      <c r="J28" s="7">
         <f t="shared" si="4"/>
         <v>1.4410563149638933E-2</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="7">
         <v>5.9555999999999998E-2</v>
       </c>
-      <c r="L28" s="5">
+      <c r="L28" s="7">
         <f t="shared" si="5"/>
         <v>5.1223214600910699E-2</v>
       </c>
@@ -1753,31 +1794,31 @@
         <f t="shared" si="9"/>
         <v>ward</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="5">
         <v>0.334951</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="7">
         <f t="shared" si="2"/>
         <v>1.6867286995856056E-2</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="7">
         <v>7.2472999999999996E-2</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="7">
         <f t="shared" si="3"/>
         <v>5.4045406285905394E-2</v>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="5">
         <v>0.35316599999999998</v>
       </c>
-      <c r="J29" s="5">
+      <c r="J29" s="7">
         <f t="shared" si="4"/>
         <v>1.4617413338389618E-2</v>
       </c>
-      <c r="K29" s="5">
+      <c r="K29" s="7">
         <v>5.9521999999999999E-2</v>
       </c>
-      <c r="L29" s="5">
+      <c r="L29" s="7">
         <f t="shared" si="5"/>
         <v>5.0623080453277708E-2</v>
       </c>
@@ -1798,31 +1839,31 @@
         <f t="shared" si="9"/>
         <v>ward</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="5">
         <v>0.33504800000000001</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="7">
         <f t="shared" si="2"/>
         <v>1.7161766268461935E-2</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="7">
         <v>7.2112999999999997E-2</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="7">
         <f t="shared" si="3"/>
         <v>4.8809575752287011E-2</v>
       </c>
-      <c r="I30" s="6">
+      <c r="I30" s="5">
         <v>0.35333100000000001</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J30" s="7">
         <f t="shared" si="4"/>
         <v>1.5091445020943603E-2</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K30" s="7">
         <v>5.9318999999999997E-2</v>
       </c>
-      <c r="L30" s="5">
+      <c r="L30" s="7">
         <f t="shared" si="5"/>
         <v>4.7039926571821822E-2</v>
       </c>
@@ -1843,31 +1884,31 @@
         <f t="shared" si="9"/>
         <v>ward</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="5">
         <v>0.334621</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="7">
         <f t="shared" si="2"/>
         <v>1.5865450295238264E-2</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="7">
         <v>7.1244000000000002E-2</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="7">
         <f t="shared" si="3"/>
         <v>3.6170862603080459E-2</v>
       </c>
-      <c r="I31" s="6">
+      <c r="I31" s="5">
         <v>0.35302499999999998</v>
       </c>
-      <c r="J31" s="5">
+      <c r="J31" s="7">
         <f t="shared" si="4"/>
         <v>1.4212331718752634E-2</v>
       </c>
-      <c r="K31" s="5">
+      <c r="K31" s="7">
         <v>5.8702999999999998E-2</v>
       </c>
-      <c r="L31" s="5">
+      <c r="L31" s="7">
         <f t="shared" si="5"/>
         <v>3.6166907897059258E-2</v>
       </c>
@@ -1888,31 +1929,31 @@
         <f t="shared" si="9"/>
         <v>ward</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="5">
         <v>0.33337600000000001</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="7">
         <f t="shared" si="2"/>
         <v>1.2085793651998399E-2</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="7">
         <v>7.0335999999999996E-2</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="7">
         <f t="shared" si="3"/>
         <v>2.296493447939842E-2</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="5">
         <v>0.35219400000000001</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J32" s="7">
         <f t="shared" si="4"/>
         <v>1.1824935790253933E-2</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K32" s="7">
         <v>5.7993000000000003E-2</v>
       </c>
-      <c r="L32" s="5">
+      <c r="L32" s="7">
         <f t="shared" si="5"/>
         <v>2.363469481413492E-2</v>
       </c>
@@ -1933,31 +1974,31 @@
         <f t="shared" si="9"/>
         <v>ward</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="5">
         <v>0.33205099999999999</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="7">
         <f t="shared" si="2"/>
         <v>8.0632675055783837E-3</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="7">
         <v>6.9447999999999996E-2</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="7">
         <f t="shared" si="3"/>
         <v>1.004988582980638E-2</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="5">
         <v>0.35130800000000001</v>
       </c>
-      <c r="J33" s="5">
+      <c r="J33" s="7">
         <f t="shared" si="4"/>
         <v>9.2795293009038504E-3</v>
       </c>
-      <c r="K33" s="5">
+      <c r="K33" s="7">
         <v>5.7251000000000003E-2</v>
       </c>
-      <c r="L33" s="5">
+      <c r="L33" s="7">
         <f t="shared" si="5"/>
         <v>1.0537649592261805E-2</v>
       </c>
@@ -1976,31 +2017,31 @@
       <c r="D34" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="5">
         <v>0.331617</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="7">
         <f t="shared" si="2"/>
         <v>6.7457004508265205E-3</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="7">
         <v>6.9750000000000006E-2</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="7">
         <f t="shared" si="3"/>
         <v>1.4442165888564187E-2</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <v>0.350267</v>
       </c>
-      <c r="J34" s="5">
+      <c r="J34" s="7">
         <f t="shared" si="4"/>
         <v>6.2888203218818672E-3</v>
       </c>
-      <c r="K34" s="5">
+      <c r="K34" s="7">
         <v>5.7377999999999998E-2</v>
       </c>
-      <c r="L34" s="5">
+      <c r="L34" s="7">
         <f t="shared" si="5"/>
         <v>1.2779327143714396E-2</v>
       </c>
@@ -2019,38 +2060,38 @@
       <c r="D35" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="5">
         <v>0.334013</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="7">
         <f t="shared" si="2"/>
         <v>1.4019642071069722E-2</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="7">
         <v>7.0777000000000007E-2</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="7">
         <f t="shared" si="3"/>
         <v>2.9378826883081112E-2</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="5">
         <v>0.35232000000000002</v>
       </c>
-      <c r="J35" s="5">
+      <c r="J35" s="7">
         <f t="shared" si="4"/>
         <v>1.2186923620567872E-2</v>
       </c>
-      <c r="K35" s="5">
+      <c r="K35" s="7">
         <v>5.8124000000000002E-2</v>
       </c>
-      <c r="L35" s="5">
+      <c r="L35" s="7">
         <f t="shared" si="5"/>
         <v>2.5946976382956174E-2</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A36:A67" si="10">A35+1</f>
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -2062,38 +2103,38 @@
       <c r="D36" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="5">
         <v>0.32976699999999998</v>
       </c>
-      <c r="F36" s="5">
-        <f t="shared" si="2"/>
+      <c r="F36" s="7">
+        <f t="shared" ref="F36:F67" si="11">IF(ISNUMBER(E36),(E36-E$3)/E$3,"")</f>
         <v>1.1293431897872871E-3</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="7">
         <v>6.8874000000000005E-2</v>
       </c>
-      <c r="H36" s="5">
-        <f t="shared" si="3"/>
+      <c r="H36" s="7">
+        <f t="shared" ref="H36:H67" si="12">IF(ISNUMBER(G36),(G36-G$3)/G$3,"")</f>
         <v>1.7016449234260656E-3</v>
       </c>
-      <c r="I36" s="6">
+      <c r="I36" s="5">
         <v>0.34839399999999998</v>
       </c>
-      <c r="J36" s="5">
-        <f t="shared" si="4"/>
+      <c r="J36" s="7">
+        <f t="shared" ref="J36:J67" si="13">IF(ISNUMBER(I36),(I36-I$3)/I$3,"")</f>
         <v>9.0784249507289442E-4</v>
       </c>
-      <c r="K36" s="5">
+      <c r="K36" s="7">
         <v>5.6644E-2</v>
       </c>
-      <c r="L36" s="5">
-        <f t="shared" si="5"/>
+      <c r="L36" s="7">
+        <f t="shared" ref="L36:L67" si="14">IF(ISNUMBER(K36),(K36-K$3)/K$3,"")</f>
         <v>-1.7651004342152473E-4</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -2105,38 +2146,38 @@
       <c r="D37" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="5">
         <v>0.33334200000000003</v>
       </c>
-      <c r="F37" s="5">
-        <f t="shared" si="2"/>
+      <c r="F37" s="7">
+        <f t="shared" si="11"/>
         <v>1.1982574113146932E-2</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="7">
         <v>7.0428000000000004E-2</v>
       </c>
-      <c r="H37" s="5">
-        <f t="shared" si="3"/>
+      <c r="H37" s="7">
+        <f t="shared" si="12"/>
         <v>2.4302980060212136E-2</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37" s="5">
         <v>0.35145100000000001</v>
       </c>
-      <c r="J37" s="5">
-        <f t="shared" si="4"/>
+      <c r="J37" s="7">
+        <f t="shared" si="13"/>
         <v>9.6903567591172524E-3</v>
       </c>
-      <c r="K37" s="5">
+      <c r="K37" s="7">
         <v>5.7426999999999999E-2</v>
       </c>
-      <c r="L37" s="5">
-        <f t="shared" si="5"/>
+      <c r="L37" s="7">
+        <f t="shared" si="14"/>
         <v>1.364422635647961E-2</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>35</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -2148,38 +2189,38 @@
       <c r="D38" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="5">
         <v>0.33004699999999998</v>
       </c>
-      <c r="F38" s="5">
-        <f t="shared" si="2"/>
+      <c r="F38" s="7">
+        <f t="shared" si="11"/>
         <v>1.9793864509175486E-3</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="7">
         <v>6.8934999999999996E-2</v>
       </c>
-      <c r="H38" s="5">
-        <f t="shared" si="3"/>
+      <c r="H38" s="7">
+        <f t="shared" si="12"/>
         <v>2.5888273194001718E-3</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="5">
         <v>0.34848000000000001</v>
       </c>
-      <c r="J38" s="5">
-        <f t="shared" si="4"/>
+      <c r="J38" s="7">
+        <f t="shared" si="13"/>
         <v>1.1549135538586567E-3</v>
       </c>
-      <c r="K38" s="5">
+      <c r="K38" s="7">
         <v>5.6693E-2</v>
       </c>
-      <c r="L38" s="5">
-        <f t="shared" si="5"/>
+      <c r="L38" s="7">
+        <f t="shared" si="14"/>
         <v>6.8838916934368922E-4</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -2191,38 +2232,38 @@
       <c r="D39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="5">
         <v>0.333706</v>
       </c>
-      <c r="F39" s="5">
-        <f t="shared" si="2"/>
+      <c r="F39" s="7">
+        <f t="shared" si="11"/>
         <v>1.3087630352616189E-2</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="7">
         <v>7.0527000000000006E-2</v>
       </c>
-      <c r="H39" s="5">
-        <f t="shared" si="3"/>
+      <c r="H39" s="7">
+        <f t="shared" si="12"/>
         <v>2.5742833456957222E-2</v>
       </c>
-      <c r="I39" s="6">
+      <c r="I39" s="5">
         <v>0.35141499999999998</v>
       </c>
-      <c r="J39" s="5">
-        <f t="shared" si="4"/>
+      <c r="J39" s="7">
+        <f t="shared" si="13"/>
         <v>9.5869316647417494E-3</v>
       </c>
-      <c r="K39" s="5">
+      <c r="K39" s="7">
         <v>5.7391999999999999E-2</v>
       </c>
-      <c r="L39" s="5">
-        <f t="shared" si="5"/>
+      <c r="L39" s="7">
+        <f t="shared" si="14"/>
         <v>1.3026441204504458E-2</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -2234,38 +2275,38 @@
       <c r="D40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="5">
         <v>0.32975199999999999</v>
       </c>
-      <c r="F40" s="5">
-        <f t="shared" si="2"/>
+      <c r="F40" s="7">
+        <f t="shared" si="11"/>
         <v>1.0838051579410623E-3</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="7">
         <v>6.8862999999999994E-2</v>
       </c>
-      <c r="H40" s="5">
-        <f t="shared" si="3"/>
+      <c r="H40" s="7">
+        <f t="shared" si="12"/>
         <v>1.5416612126764545E-3</v>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="5">
         <v>0.34833700000000001</v>
       </c>
-      <c r="J40" s="5">
-        <f t="shared" si="4"/>
+      <c r="J40" s="7">
+        <f t="shared" si="13"/>
         <v>7.4408609564525542E-4</v>
       </c>
-      <c r="K40" s="5">
+      <c r="K40" s="7">
         <v>5.6656999999999999E-2</v>
       </c>
-      <c r="L40" s="5">
-        <f t="shared" si="5"/>
+      <c r="L40" s="7">
+        <f t="shared" si="14"/>
         <v>5.2953013026371681E-5</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -2277,38 +2318,38 @@
       <c r="D41" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="5">
         <v>0.33386700000000002</v>
       </c>
-      <c r="F41" s="5">
-        <f t="shared" si="2"/>
+      <c r="F41" s="7">
+        <f t="shared" si="11"/>
         <v>1.3576405227766151E-2</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="7">
         <v>7.1085999999999996E-2</v>
       </c>
-      <c r="H41" s="5">
-        <f t="shared" si="3"/>
+      <c r="H41" s="7">
+        <f t="shared" si="12"/>
         <v>3.3872914757770087E-2</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="5">
         <v>0.35150700000000001</v>
       </c>
-      <c r="J41" s="5">
-        <f t="shared" si="4"/>
+      <c r="J41" s="7">
+        <f t="shared" si="13"/>
         <v>9.8512402392567627E-3</v>
       </c>
-      <c r="K41" s="5">
+      <c r="K41" s="7">
         <v>5.7704999999999999E-2</v>
       </c>
-      <c r="L41" s="5">
-        <f t="shared" si="5"/>
+      <c r="L41" s="7">
+        <f t="shared" si="14"/>
         <v>1.8551205563596504E-2</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -2320,38 +2361,38 @@
       <c r="D42" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42" s="5">
         <v>0.32972499999999999</v>
       </c>
-      <c r="F42" s="5">
-        <f t="shared" si="2"/>
+      <c r="F42" s="7">
+        <f t="shared" si="11"/>
         <v>1.00183670061779E-3</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="7">
         <v>6.8848000000000006E-2</v>
       </c>
-      <c r="H42" s="5">
-        <f t="shared" si="3"/>
+      <c r="H42" s="7">
+        <f t="shared" si="12"/>
         <v>1.323501607109207E-3</v>
       </c>
-      <c r="I42" s="6">
+      <c r="I42" s="5">
         <v>0.34833700000000001</v>
       </c>
-      <c r="J42" s="5">
-        <f t="shared" si="4"/>
+      <c r="J42" s="7">
+        <f t="shared" si="13"/>
         <v>7.4408609564525542E-4</v>
       </c>
-      <c r="K42" s="5">
+      <c r="K42" s="7">
         <v>5.6633000000000003E-2</v>
       </c>
-      <c r="L42" s="5">
-        <f t="shared" si="5"/>
+      <c r="L42" s="7">
+        <f t="shared" si="14"/>
         <v>-3.7067109118509169E-4</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -2363,38 +2404,38 @@
       <c r="D43" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="5">
         <v>0.33396900000000002</v>
       </c>
-      <c r="F43" s="5">
-        <f t="shared" si="2"/>
+      <c r="F43" s="7">
+        <f t="shared" si="11"/>
         <v>1.3886063844320716E-2</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="7">
         <v>7.1175000000000002E-2</v>
       </c>
-      <c r="H43" s="5">
-        <f t="shared" si="3"/>
+      <c r="H43" s="7">
+        <f t="shared" si="12"/>
         <v>3.5167328417470271E-2</v>
       </c>
-      <c r="I43" s="6">
+      <c r="I43" s="5">
         <v>0.35150999999999999</v>
       </c>
-      <c r="J43" s="5">
-        <f t="shared" si="4"/>
+      <c r="J43" s="7">
+        <f t="shared" si="13"/>
         <v>9.8598589971213083E-3</v>
       </c>
-      <c r="K43" s="5">
+      <c r="K43" s="7">
         <v>5.7682999999999998E-2</v>
       </c>
-      <c r="L43" s="5">
-        <f t="shared" si="5"/>
+      <c r="L43" s="7">
+        <f t="shared" si="14"/>
         <v>1.8162883468069248E-2</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>41</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -2406,38 +2447,38 @@
       <c r="D44" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E44" s="5">
         <v>0.32963900000000002</v>
       </c>
-      <c r="F44" s="5">
-        <f t="shared" si="2"/>
+      <c r="F44" s="7">
+        <f t="shared" si="11"/>
         <v>7.4075198469928803E-4</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="7">
         <v>6.8828E-2</v>
       </c>
-      <c r="H44" s="5">
-        <f t="shared" si="3"/>
+      <c r="H44" s="7">
+        <f t="shared" si="12"/>
         <v>1.0326221330192069E-3</v>
       </c>
-      <c r="I44" s="6">
+      <c r="I44" s="5">
         <v>0.348244</v>
       </c>
-      <c r="J44" s="5">
-        <f t="shared" si="4"/>
+      <c r="J44" s="7">
+        <f t="shared" si="13"/>
         <v>4.7690460184211434E-4</v>
       </c>
-      <c r="K44" s="5">
+      <c r="K44" s="7">
         <v>5.6640999999999997E-2</v>
       </c>
-      <c r="L44" s="5">
-        <f t="shared" si="5"/>
+      <c r="L44" s="7">
+        <f t="shared" si="14"/>
         <v>-2.2946305644801888E-4</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>42</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -2449,38 +2490,38 @@
       <c r="D45" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="5">
         <v>0.33421899999999999</v>
       </c>
-      <c r="F45" s="5">
-        <f t="shared" si="2"/>
+      <c r="F45" s="7">
+        <f t="shared" si="11"/>
         <v>1.464503104175836E-2</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="7">
         <v>7.1684999999999999E-2</v>
       </c>
-      <c r="H45" s="5">
-        <f t="shared" si="3"/>
+      <c r="H45" s="7">
+        <f t="shared" si="12"/>
         <v>4.2584755006762946E-2</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45" s="5">
         <v>0.351746</v>
       </c>
-      <c r="J45" s="5">
-        <f t="shared" si="4"/>
+      <c r="J45" s="7">
+        <f t="shared" si="13"/>
         <v>1.0537867949137851E-2</v>
       </c>
-      <c r="K45" s="5">
+      <c r="K45" s="7">
         <v>5.8206000000000001E-2</v>
       </c>
-      <c r="L45" s="5">
-        <f t="shared" si="5"/>
+      <c r="L45" s="7">
+        <f t="shared" si="14"/>
         <v>2.739435873901221E-2</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>43</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -2492,38 +2533,38 @@
       <c r="D46" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="5">
         <v>0.32957399999999998</v>
       </c>
-      <c r="F46" s="5">
-        <f t="shared" si="2"/>
+      <c r="F46" s="7">
+        <f t="shared" si="11"/>
         <v>5.4342051336536603E-4</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="7">
         <v>6.8798999999999999E-2</v>
       </c>
-      <c r="H46" s="5">
-        <f t="shared" si="3"/>
+      <c r="H46" s="7">
+        <f t="shared" si="12"/>
         <v>6.1084689558881813E-4</v>
       </c>
-      <c r="I46" s="6">
+      <c r="I46" s="5">
         <v>0.34819499999999998</v>
       </c>
-      <c r="J46" s="5">
-        <f t="shared" si="4"/>
+      <c r="J46" s="7">
+        <f t="shared" si="13"/>
         <v>3.3613155671998298E-4</v>
       </c>
-      <c r="K46" s="5">
+      <c r="K46" s="7">
         <v>5.6610000000000001E-2</v>
       </c>
-      <c r="L46" s="5">
-        <f t="shared" si="5"/>
+      <c r="L46" s="7">
+        <f t="shared" si="14"/>
         <v>-7.7664419105451276E-4</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>44</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -2535,38 +2576,38 @@
       <c r="D47" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E47" s="5">
         <v>0.33448600000000001</v>
       </c>
-      <c r="F47" s="5">
-        <f t="shared" si="2"/>
+      <c r="F47" s="7">
+        <f t="shared" si="11"/>
         <v>1.5455608008621904E-2</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="7">
         <v>7.1938000000000002E-2</v>
       </c>
-      <c r="H47" s="5">
-        <f t="shared" si="3"/>
+      <c r="H47" s="7">
+        <f t="shared" si="12"/>
         <v>4.6264380354000371E-2</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I47" s="5">
         <v>0.35190199999999999</v>
       </c>
-      <c r="J47" s="5">
-        <f t="shared" si="4"/>
+      <c r="J47" s="7">
+        <f t="shared" si="13"/>
         <v>1.098604335809788E-2</v>
       </c>
-      <c r="K47" s="5">
+      <c r="K47" s="7">
         <v>5.8455E-2</v>
       </c>
-      <c r="L47" s="5">
-        <f t="shared" si="5"/>
+      <c r="L47" s="7">
+        <f t="shared" si="14"/>
         <v>3.1789458820206819E-2</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>45</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -2578,38 +2619,38 @@
       <c r="D48" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="5">
         <v>0.32950600000000002</v>
       </c>
-      <c r="F48" s="5">
-        <f t="shared" si="2"/>
+      <c r="F48" s="7">
+        <f t="shared" si="11"/>
         <v>3.3698143566243492E-4</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="7">
         <v>6.8784999999999999E-2</v>
       </c>
-      <c r="H48" s="5">
-        <f t="shared" si="3"/>
+      <c r="H48" s="7">
+        <f t="shared" si="12"/>
         <v>4.0723126372587879E-4</v>
       </c>
-      <c r="I48" s="6">
+      <c r="I48" s="5">
         <v>0.34812199999999999</v>
       </c>
-      <c r="J48" s="5">
-        <f t="shared" si="4"/>
+      <c r="J48" s="7">
+        <f t="shared" si="13"/>
         <v>1.2640844868100969E-4</v>
       </c>
-      <c r="K48" s="5">
+      <c r="K48" s="7">
         <v>5.6612999999999997E-2</v>
       </c>
-      <c r="L48" s="5">
-        <f t="shared" si="5"/>
+      <c r="L48" s="7">
+        <f t="shared" si="14"/>
         <v>-7.236911780281411E-4</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>46</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -2621,79 +2662,2325 @@
       <c r="D49" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E49" s="5">
         <v>0.33446999999999999</v>
       </c>
-      <c r="F49" s="5">
-        <f t="shared" si="2"/>
+      <c r="F49" s="7">
+        <f t="shared" si="11"/>
         <v>1.5407034107985841E-2</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49" s="7">
         <v>7.2139999999999996E-2</v>
       </c>
-      <c r="H49" s="5">
-        <f t="shared" si="3"/>
+      <c r="H49" s="7">
+        <f t="shared" si="12"/>
         <v>4.9202263042308375E-2</v>
       </c>
-      <c r="I49" s="6">
+      <c r="I49" s="5">
         <v>0.352074</v>
       </c>
-      <c r="J49" s="5">
-        <f t="shared" si="4"/>
+      <c r="J49" s="7">
+        <f t="shared" si="13"/>
         <v>1.1480185475669246E-2</v>
       </c>
-      <c r="K49" s="5">
+      <c r="K49" s="7">
         <v>5.8744999999999999E-2</v>
       </c>
-      <c r="L49" s="5">
-        <f t="shared" si="5"/>
+      <c r="L49" s="7">
+        <f t="shared" si="14"/>
         <v>3.6908250079429439E-2</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="4">
+        <f t="shared" si="10"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
+      <c r="C50" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="5">
+        <v>0.33396900000000002</v>
+      </c>
+      <c r="F50" s="7">
+        <f t="shared" si="11"/>
+        <v>1.3886063844320716E-2</v>
+      </c>
+      <c r="G50" s="7">
+        <v>7.1105000000000002E-2</v>
+      </c>
+      <c r="H50" s="7">
+        <f t="shared" si="12"/>
+        <v>3.4149250258155572E-2</v>
+      </c>
+      <c r="I50" s="5">
+        <v>0.35181099999999998</v>
+      </c>
+      <c r="J50" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0724607702871156E-2</v>
+      </c>
+      <c r="K50" s="7">
+        <v>5.7895000000000002E-2</v>
+      </c>
+      <c r="L50" s="7">
+        <f t="shared" si="14"/>
+        <v>2.1904896388604492E-2</v>
+      </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="4">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
+      <c r="E51" s="5">
+        <v>0.332843</v>
+      </c>
+      <c r="F51" s="7">
+        <f t="shared" si="11"/>
+        <v>1.0467675587061147E-2</v>
+      </c>
+      <c r="G51" s="7">
+        <v>7.0045999999999997E-2</v>
+      </c>
+      <c r="H51" s="7">
+        <f t="shared" si="12"/>
+        <v>1.8747182105094733E-2</v>
+      </c>
+      <c r="I51" s="5">
+        <v>0.35064600000000001</v>
+      </c>
+      <c r="J51" s="7">
+        <f t="shared" si="13"/>
+        <v>7.3776567321118102E-3</v>
+      </c>
+      <c r="K51" s="7">
+        <v>5.6985000000000001E-2</v>
+      </c>
+      <c r="L51" s="7">
+        <f t="shared" si="14"/>
+        <v>5.8424824372506432E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <f t="shared" si="10"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" s="5">
+        <v>0.33098899999999998</v>
+      </c>
+      <c r="F52" s="7">
+        <f t="shared" si="11"/>
+        <v>4.8391748508628983E-3</v>
+      </c>
+      <c r="G52" s="7">
+        <v>6.8986000000000006E-2</v>
+      </c>
+      <c r="H52" s="7">
+        <f t="shared" si="12"/>
+        <v>3.3305699783295808E-3</v>
+      </c>
+      <c r="I52" s="5">
+        <v>0.34893099999999999</v>
+      </c>
+      <c r="J52" s="7">
+        <f t="shared" si="13"/>
+        <v>2.4506001528392849E-3</v>
+      </c>
+      <c r="K52" s="7">
+        <v>5.6350999999999998E-2</v>
+      </c>
+      <c r="L52" s="7">
+        <f t="shared" si="14"/>
+        <v>-5.3482543156706435E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <f t="shared" si="10"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="5">
+        <v>0.32936500000000002</v>
+      </c>
+      <c r="F53" s="7">
+        <f t="shared" si="11"/>
+        <v>-9.1076063692449772E-5</v>
+      </c>
+      <c r="G53" s="7">
+        <v>6.8325999999999998E-2</v>
+      </c>
+      <c r="H53" s="7">
+        <f t="shared" si="12"/>
+        <v>-6.2684526666375905E-3</v>
+      </c>
+      <c r="I53" s="5">
+        <v>0.34787499999999999</v>
+      </c>
+      <c r="J53" s="7">
+        <f t="shared" si="13"/>
+        <v>-5.8320261550574501E-4</v>
+      </c>
+      <c r="K53" s="7">
+        <v>5.6148000000000003E-2</v>
+      </c>
+      <c r="L53" s="7">
+        <f t="shared" si="14"/>
+        <v>-8.9314081971264073E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
+        <f t="shared" si="10"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="5">
+        <v>0.32938299999999998</v>
+      </c>
+      <c r="F54" s="7">
+        <f t="shared" si="11"/>
+        <v>-3.6430425477047321E-5</v>
+      </c>
+      <c r="G54" s="7">
+        <v>6.8590999999999999E-2</v>
+      </c>
+      <c r="H54" s="7">
+        <f t="shared" si="12"/>
+        <v>-2.4142996349462527E-3</v>
+      </c>
+      <c r="I54" s="5">
+        <v>0.34801399999999999</v>
+      </c>
+      <c r="J54" s="7">
+        <f t="shared" si="13"/>
+        <v>-1.8386683444517751E-4</v>
+      </c>
+      <c r="K54" s="7">
+        <v>5.6502999999999998E-2</v>
+      </c>
+      <c r="L54" s="7">
+        <f t="shared" si="14"/>
+        <v>-2.6653016556643008E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
+        <f t="shared" si="10"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="5">
+        <v>0.32940799999999998</v>
+      </c>
+      <c r="F55" s="7">
+        <f t="shared" si="11"/>
+        <v>3.9466294266716996E-5</v>
+      </c>
+      <c r="G55" s="7">
+        <v>6.8752999999999995E-2</v>
+      </c>
+      <c r="H55" s="7">
+        <f t="shared" si="12"/>
+        <v>-5.8175894818040355E-5</v>
+      </c>
+      <c r="I55" s="5">
+        <v>0.34809699999999999</v>
+      </c>
+      <c r="J55" s="7">
+        <f t="shared" si="13"/>
+        <v>5.4585466475879679E-5</v>
+      </c>
+      <c r="K55" s="7">
+        <v>5.6647000000000003E-2</v>
+      </c>
+      <c r="L55" s="7">
+        <f t="shared" si="14"/>
+        <v>-1.2355703039503056E-4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
+        <f t="shared" si="10"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="5">
+        <v>0.33375300000000002</v>
+      </c>
+      <c r="F56" s="7">
+        <f t="shared" si="11"/>
+        <v>1.323031618573454E-2</v>
+      </c>
+      <c r="G56" s="7">
+        <v>7.1399000000000004E-2</v>
+      </c>
+      <c r="H56" s="7">
+        <f t="shared" si="12"/>
+        <v>3.8425178527277302E-2</v>
+      </c>
+      <c r="I56" s="5">
+        <v>0.35173900000000002</v>
+      </c>
+      <c r="J56" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0517757514120471E-2</v>
+      </c>
+      <c r="K56" s="7">
+        <v>5.8187999999999997E-2</v>
+      </c>
+      <c r="L56" s="7">
+        <f t="shared" si="14"/>
+        <v>2.7076640660853489E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
+        <f t="shared" si="10"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="5">
+        <v>0.33384399999999997</v>
+      </c>
+      <c r="F57" s="7">
+        <f t="shared" si="11"/>
+        <v>1.3506580245601727E-2</v>
+      </c>
+      <c r="G57" s="7">
+        <v>7.1010000000000004E-2</v>
+      </c>
+      <c r="H57" s="7">
+        <f t="shared" si="12"/>
+        <v>3.2767572756228533E-2</v>
+      </c>
+      <c r="I57" s="5">
+        <v>0.35187800000000002</v>
+      </c>
+      <c r="J57" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0917093295181039E-2</v>
+      </c>
+      <c r="K57" s="7">
+        <v>5.7889000000000003E-2</v>
+      </c>
+      <c r="L57" s="7">
+        <f t="shared" si="14"/>
+        <v>2.1798990362551628E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
+        <f t="shared" si="10"/>
+        <v>55</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="5">
+        <v>0.33388699999999999</v>
+      </c>
+      <c r="F58" s="7">
+        <f t="shared" si="11"/>
+        <v>1.3637122603561062E-2</v>
+      </c>
+      <c r="G58" s="7">
+        <v>7.0430999999999994E-2</v>
+      </c>
+      <c r="H58" s="7">
+        <f t="shared" si="12"/>
+        <v>2.4346611981325466E-2</v>
+      </c>
+      <c r="I58" s="5">
+        <v>0.35193600000000003</v>
+      </c>
+      <c r="J58" s="7">
+        <f t="shared" si="13"/>
+        <v>1.1083722613896965E-2</v>
+      </c>
+      <c r="K58" s="7">
+        <v>5.7410999999999997E-2</v>
+      </c>
+      <c r="L58" s="7">
+        <f t="shared" si="14"/>
+        <v>1.336181028700522E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
+        <f t="shared" si="10"/>
+        <v>56</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="5">
+        <v>0.33364300000000002</v>
+      </c>
+      <c r="F59" s="7">
+        <f t="shared" si="11"/>
+        <v>1.2896370618861943E-2</v>
+      </c>
+      <c r="G59" s="7">
+        <v>6.9750999999999994E-2</v>
+      </c>
+      <c r="H59" s="7">
+        <f t="shared" si="12"/>
+        <v>1.4456709862268494E-2</v>
+      </c>
+      <c r="I59" s="5">
+        <v>0.351522</v>
+      </c>
+      <c r="J59" s="7">
+        <f t="shared" si="13"/>
+        <v>9.8943340285798081E-3</v>
+      </c>
+      <c r="K59" s="7">
+        <v>5.6753999999999999E-2</v>
+      </c>
+      <c r="L59" s="7">
+        <f t="shared" si="14"/>
+        <v>1.7651004342146349E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
+        <f t="shared" si="10"/>
+        <v>57</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="5">
+        <v>0.33263700000000002</v>
+      </c>
+      <c r="F60" s="7">
+        <f t="shared" si="11"/>
+        <v>9.842286616372509E-3</v>
+      </c>
+      <c r="G60" s="7">
+        <v>6.9163000000000002E-2</v>
+      </c>
+      <c r="H60" s="7">
+        <f t="shared" si="12"/>
+        <v>5.9048533240252422E-3</v>
+      </c>
+      <c r="I60" s="5">
+        <v>0.35077199999999997</v>
+      </c>
+      <c r="J60" s="7">
+        <f t="shared" si="13"/>
+        <v>7.7396445624255891E-3</v>
+      </c>
+      <c r="K60" s="7">
+        <v>5.6494999999999997E-2</v>
+      </c>
+      <c r="L60" s="7">
+        <f t="shared" si="14"/>
+        <v>-2.806509690401496E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <f t="shared" si="10"/>
+        <v>58</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="5">
+        <v>0.33035300000000001</v>
+      </c>
+      <c r="F61" s="7">
+        <f t="shared" si="11"/>
+        <v>2.9083623005814125E-3</v>
+      </c>
+      <c r="G61" s="7">
+        <v>6.8856000000000001E-2</v>
+      </c>
+      <c r="H61" s="7">
+        <f t="shared" si="12"/>
+        <v>1.4398533967450858E-3</v>
+      </c>
+      <c r="I61" s="5">
+        <v>0.34895500000000002</v>
+      </c>
+      <c r="J61" s="7">
+        <f t="shared" si="13"/>
+        <v>2.5195502157562863E-3</v>
+      </c>
+      <c r="K61" s="7">
+        <v>5.6751999999999997E-2</v>
+      </c>
+      <c r="L61" s="7">
+        <f t="shared" si="14"/>
+        <v>1.7297984255303053E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
+        <f t="shared" si="10"/>
+        <v>59</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="5">
+        <v>0.33387899999999998</v>
+      </c>
+      <c r="F62" s="7">
+        <f t="shared" si="11"/>
+        <v>1.3612835653243031E-2</v>
+      </c>
+      <c r="G62" s="7">
+        <v>7.1365999999999999E-2</v>
+      </c>
+      <c r="H62" s="7">
+        <f t="shared" si="12"/>
+        <v>3.7945227395028876E-2</v>
+      </c>
+      <c r="I62" s="5">
+        <v>0.35187000000000002</v>
+      </c>
+      <c r="J62" s="7">
+        <f t="shared" si="13"/>
+        <v>1.0894109940875371E-2</v>
+      </c>
+      <c r="K62" s="7">
+        <v>5.8173999999999997E-2</v>
+      </c>
+      <c r="L62" s="7">
+        <f t="shared" si="14"/>
+        <v>2.6829526600063429E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="5">
+        <v>0.33396799999999999</v>
+      </c>
+      <c r="F63" s="7">
+        <f t="shared" si="11"/>
+        <v>1.3883027975530879E-2</v>
+      </c>
+      <c r="G63" s="7">
+        <v>7.0896000000000001E-2</v>
+      </c>
+      <c r="H63" s="7">
+        <f t="shared" si="12"/>
+        <v>3.1109559753915994E-2</v>
+      </c>
+      <c r="I63" s="5">
+        <v>0.35205500000000001</v>
+      </c>
+      <c r="J63" s="7">
+        <f t="shared" si="13"/>
+        <v>1.1425600009193366E-2</v>
+      </c>
+      <c r="K63" s="7">
+        <v>5.7854000000000003E-2</v>
+      </c>
+      <c r="L63" s="7">
+        <f t="shared" si="14"/>
+        <v>2.1181205210576474E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" s="4">
+        <f t="shared" si="10"/>
+        <v>61</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="5">
+        <v>0.33371099999999998</v>
+      </c>
+      <c r="F64" s="7">
+        <f t="shared" si="11"/>
+        <v>1.3102809696564873E-2</v>
+      </c>
+      <c r="G64" s="7">
+        <v>7.0084999999999995E-2</v>
+      </c>
+      <c r="H64" s="7">
+        <f t="shared" si="12"/>
+        <v>1.9314397079570021E-2</v>
+      </c>
+      <c r="I64" s="5">
+        <v>0.35167700000000002</v>
+      </c>
+      <c r="J64" s="7">
+        <f t="shared" si="13"/>
+        <v>1.033963651825171E-2</v>
+      </c>
+      <c r="K64" s="7">
+        <v>5.7105999999999997E-2</v>
+      </c>
+      <c r="L64" s="7">
+        <f t="shared" si="14"/>
+        <v>7.9782539626503703E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
+        <f t="shared" si="10"/>
+        <v>62</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C65" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="5">
+        <v>0.33251599999999998</v>
+      </c>
+      <c r="F65" s="7">
+        <f t="shared" si="11"/>
+        <v>9.4749464928125353E-3</v>
+      </c>
+      <c r="G65" s="7">
+        <v>6.9231000000000001E-2</v>
+      </c>
+      <c r="H65" s="7">
+        <f t="shared" si="12"/>
+        <v>6.8938435359309188E-3</v>
+      </c>
+      <c r="I65" s="5">
+        <v>0.350356</v>
+      </c>
+      <c r="J65" s="7">
+        <f t="shared" si="13"/>
+        <v>6.5445101385321744E-3</v>
+      </c>
+      <c r="K65" s="7">
+        <v>5.6188000000000002E-2</v>
+      </c>
+      <c r="L65" s="7">
+        <f t="shared" si="14"/>
+        <v>-8.2253680234405536E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="4">
+        <f t="shared" si="10"/>
+        <v>63</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="5">
+        <v>0.33008799999999999</v>
+      </c>
+      <c r="F66" s="7">
+        <f t="shared" si="11"/>
+        <v>2.1038570712973762E-3</v>
+      </c>
+      <c r="G66" s="7">
+        <v>6.8650000000000003E-2</v>
+      </c>
+      <c r="H66" s="7">
+        <f t="shared" si="12"/>
+        <v>-1.5562051863809647E-3</v>
+      </c>
+      <c r="I66" s="5">
+        <v>0.34834300000000001</v>
+      </c>
+      <c r="J66" s="7">
+        <f t="shared" si="13"/>
+        <v>7.6132361137450576E-4</v>
+      </c>
+      <c r="K66" s="7">
+        <v>5.6271000000000002E-2</v>
+      </c>
+      <c r="L66" s="7">
+        <f t="shared" si="14"/>
+        <v>-6.7603346630423517E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="4">
+        <f t="shared" si="10"/>
+        <v>64</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="5">
+        <v>0.32946999999999999</v>
+      </c>
+      <c r="F67" s="7">
+        <f t="shared" si="11"/>
+        <v>2.2769015923129296E-4</v>
+      </c>
+      <c r="G67" s="7">
+        <v>6.8756999999999999E-2</v>
+      </c>
+      <c r="H67" s="7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I67" s="5">
+        <v>0.34810000000000002</v>
+      </c>
+      <c r="J67" s="7">
+        <f t="shared" si="13"/>
+        <v>6.3204224340584588E-5</v>
+      </c>
+      <c r="K67" s="7">
+        <v>5.6626000000000003E-2</v>
+      </c>
+      <c r="L67" s="7">
+        <f t="shared" si="14"/>
+        <v>-4.9422812158012226E-4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="4">
+        <f t="shared" ref="A68:A99" si="15">A67+1</f>
+        <v>65</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C68" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" s="5">
+        <v>0.333841</v>
+      </c>
+      <c r="F68" s="7">
+        <f t="shared" ref="F68:F99" si="16">IF(ISNUMBER(E68),(E68-E$3)/E$3,"")</f>
+        <v>1.3497472639232549E-2</v>
+      </c>
+      <c r="G68" s="7">
+        <v>7.1333999999999995E-2</v>
+      </c>
+      <c r="H68" s="7">
+        <f t="shared" ref="H68:H99" si="17">IF(ISNUMBER(G68),(G68-G$3)/G$3,"")</f>
+        <v>3.7479820236484954E-2</v>
+      </c>
+      <c r="I68" s="5">
+        <v>0.35183999999999999</v>
+      </c>
+      <c r="J68" s="7">
+        <f t="shared" ref="J68:J99" si="18">IF(ISNUMBER(I68),(I68-I$3)/I$3,"")</f>
+        <v>1.0807922362229119E-2</v>
+      </c>
+      <c r="K68" s="7">
+        <v>5.8139000000000003E-2</v>
+      </c>
+      <c r="L68" s="7">
+        <f t="shared" ref="L68:L99" si="19">IF(ISNUMBER(K68),(K68-K$3)/K$3,"")</f>
+        <v>2.62117414480884E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="4">
+        <f t="shared" si="15"/>
+        <v>66</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" s="5">
+        <v>0.333951</v>
+      </c>
+      <c r="F69" s="7">
+        <f t="shared" si="16"/>
+        <v>1.3831418206105147E-2</v>
+      </c>
+      <c r="G69" s="7">
+        <v>7.0910000000000001E-2</v>
+      </c>
+      <c r="H69" s="7">
+        <f t="shared" si="17"/>
+        <v>3.1313175385778935E-2</v>
+      </c>
+      <c r="I69" s="5">
+        <v>0.352024</v>
+      </c>
+      <c r="J69" s="7">
+        <f t="shared" si="18"/>
+        <v>1.1336539511258984E-2</v>
+      </c>
+      <c r="K69" s="7">
+        <v>5.7868999999999997E-2</v>
+      </c>
+      <c r="L69" s="7">
+        <f t="shared" si="19"/>
+        <v>2.1445970275708579E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="4">
+        <f t="shared" si="15"/>
+        <v>67</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" s="5">
+        <v>0.33364899999999997</v>
+      </c>
+      <c r="F70" s="7">
+        <f t="shared" si="16"/>
+        <v>1.2914585831600298E-2</v>
+      </c>
+      <c r="G70" s="7">
+        <v>7.0016999999999996E-2</v>
+      </c>
+      <c r="H70" s="7">
+        <f t="shared" si="17"/>
+        <v>1.8325406867664342E-2</v>
+      </c>
+      <c r="I70" s="5">
+        <v>0.35161700000000001</v>
+      </c>
+      <c r="J70" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0167261360959367E-2</v>
+      </c>
+      <c r="K70" s="7">
+        <v>5.7055000000000002E-2</v>
+      </c>
+      <c r="L70" s="7">
+        <f t="shared" si="19"/>
+        <v>7.0780527412009492E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="4">
+        <f t="shared" si="15"/>
+        <v>68</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E71" s="5">
+        <v>0.332509</v>
+      </c>
+      <c r="F71" s="7">
+        <f t="shared" si="16"/>
+        <v>9.4536954112843415E-3</v>
+      </c>
+      <c r="G71" s="7">
+        <v>6.9116999999999998E-2</v>
+      </c>
+      <c r="H71" s="7">
+        <f t="shared" si="17"/>
+        <v>5.2358305336183842E-3</v>
+      </c>
+      <c r="I71" s="5">
+        <v>0.35034500000000002</v>
+      </c>
+      <c r="J71" s="7">
+        <f t="shared" si="18"/>
+        <v>6.5129080263619616E-3</v>
+      </c>
+      <c r="K71" s="7">
+        <v>5.6043999999999997E-2</v>
+      </c>
+      <c r="L71" s="7">
+        <f t="shared" si="19"/>
+        <v>-1.0767112648709824E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="4">
+        <f t="shared" si="15"/>
+        <v>69</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72" s="5">
+        <v>0.33036599999999999</v>
+      </c>
+      <c r="F72" s="7">
+        <f t="shared" si="16"/>
+        <v>2.9478285948481295E-3</v>
+      </c>
+      <c r="G72" s="7">
+        <v>6.8724999999999994E-2</v>
+      </c>
+      <c r="H72" s="7">
+        <f t="shared" si="17"/>
+        <v>-4.6540715854391913E-4</v>
+      </c>
+      <c r="I72" s="5">
+        <v>0.34846199999999999</v>
+      </c>
+      <c r="J72" s="7">
+        <f t="shared" si="18"/>
+        <v>1.1032010066709056E-3</v>
+      </c>
+      <c r="K72" s="7">
+        <v>5.6258000000000002E-2</v>
+      </c>
+      <c r="L72" s="7">
+        <f t="shared" si="19"/>
+        <v>-6.9897977194902476E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="4">
+        <f t="shared" si="15"/>
+        <v>70</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" s="5">
+        <v>0.32948300000000003</v>
+      </c>
+      <c r="F73" s="7">
+        <f t="shared" si="16"/>
+        <v>2.6715645349817846E-4</v>
+      </c>
+      <c r="G73" s="7">
+        <v>6.8770999999999999E-2</v>
+      </c>
+      <c r="H73" s="7">
+        <f t="shared" si="17"/>
+        <v>2.0361563186293939E-4</v>
+      </c>
+      <c r="I73" s="5">
+        <v>0.34811799999999998</v>
+      </c>
+      <c r="J73" s="7">
+        <f t="shared" si="18"/>
+        <v>1.1491677152817614E-4</v>
+      </c>
+      <c r="K73" s="7">
+        <v>5.6651E-2</v>
+      </c>
+      <c r="L73" s="7">
+        <f t="shared" si="19"/>
+        <v>-5.2953013026494162E-5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="4">
+        <f t="shared" si="15"/>
+        <v>71</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="5">
+        <v>0.33376099999999997</v>
+      </c>
+      <c r="F74" s="7">
+        <f t="shared" si="16"/>
+        <v>1.3254603136052402E-2</v>
+      </c>
+      <c r="G74" s="7">
+        <v>7.1417999999999995E-2</v>
+      </c>
+      <c r="H74" s="7">
+        <f t="shared" si="17"/>
+        <v>3.8701514027662594E-2</v>
+      </c>
+      <c r="I74" s="5">
+        <v>0.35173900000000002</v>
+      </c>
+      <c r="J74" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0517757514120471E-2</v>
+      </c>
+      <c r="K74" s="7">
+        <v>5.8195999999999998E-2</v>
+      </c>
+      <c r="L74" s="7">
+        <f t="shared" si="19"/>
+        <v>2.7217848695590685E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="4">
+        <f t="shared" si="15"/>
+        <v>72</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" s="5">
+        <v>0.333816</v>
+      </c>
+      <c r="F75" s="7">
+        <f t="shared" si="16"/>
+        <v>1.3421575919488785E-2</v>
+      </c>
+      <c r="G75" s="7">
+        <v>7.1010000000000004E-2</v>
+      </c>
+      <c r="H75" s="7">
+        <f t="shared" si="17"/>
+        <v>3.2767572756228533E-2</v>
+      </c>
+      <c r="I75" s="5">
+        <v>0.35186000000000001</v>
+      </c>
+      <c r="J75" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0865380747993288E-2</v>
+      </c>
+      <c r="K75" s="7">
+        <v>5.7917000000000003E-2</v>
+      </c>
+      <c r="L75" s="7">
+        <f t="shared" si="19"/>
+        <v>2.2293218484131749E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="4">
+        <f t="shared" si="15"/>
+        <v>73</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76" s="5">
+        <v>0.33374799999999999</v>
+      </c>
+      <c r="F76" s="7">
+        <f t="shared" si="16"/>
+        <v>1.3215136841785685E-2</v>
+      </c>
+      <c r="G76" s="7">
+        <v>7.0391999999999996E-2</v>
+      </c>
+      <c r="H76" s="7">
+        <f t="shared" si="17"/>
+        <v>2.3779397006850177E-2</v>
+      </c>
+      <c r="I76" s="5">
+        <v>0.35179899999999997</v>
+      </c>
+      <c r="J76" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0690132671412656E-2</v>
+      </c>
+      <c r="K76" s="7">
+        <v>5.7376999999999997E-2</v>
+      </c>
+      <c r="L76" s="7">
+        <f t="shared" si="19"/>
+        <v>1.2761676139372232E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="4">
+        <f t="shared" si="15"/>
+        <v>74</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E77" s="5">
+        <v>0.33357399999999998</v>
+      </c>
+      <c r="F77" s="7">
+        <f t="shared" si="16"/>
+        <v>1.2686895672369004E-2</v>
+      </c>
+      <c r="G77" s="7">
+        <v>6.9806999999999994E-2</v>
+      </c>
+      <c r="H77" s="7">
+        <f t="shared" si="17"/>
+        <v>1.5271172389720252E-2</v>
+      </c>
+      <c r="I77" s="5">
+        <v>0.35145700000000002</v>
+      </c>
+      <c r="J77" s="7">
+        <f t="shared" si="18"/>
+        <v>9.7075942748465031E-3</v>
+      </c>
+      <c r="K77" s="7">
+        <v>5.6917000000000002E-2</v>
+      </c>
+      <c r="L77" s="7">
+        <f t="shared" si="19"/>
+        <v>4.6422141419846675E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="4">
+        <f t="shared" si="15"/>
+        <v>75</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E78" s="5">
+        <v>0.33294000000000001</v>
+      </c>
+      <c r="F78" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0762154859667028E-2</v>
+      </c>
+      <c r="G78" s="7">
+        <v>6.9307999999999995E-2</v>
+      </c>
+      <c r="H78" s="7">
+        <f t="shared" si="17"/>
+        <v>8.0137295111769851E-3</v>
+      </c>
+      <c r="I78" s="5">
+        <v>0.35111300000000001</v>
+      </c>
+      <c r="J78" s="7">
+        <f t="shared" si="18"/>
+        <v>8.7193100397037725E-3</v>
+      </c>
+      <c r="K78" s="7">
+        <v>5.6582E-2</v>
+      </c>
+      <c r="L78" s="7">
+        <f t="shared" si="19"/>
+        <v>-1.2708723126346351E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="4">
+        <f t="shared" si="15"/>
+        <v>76</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C79" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E79" s="5">
+        <v>0.33130300000000001</v>
+      </c>
+      <c r="F79" s="7">
+        <f t="shared" si="16"/>
+        <v>5.792437650844794E-3</v>
+      </c>
+      <c r="G79" s="7">
+        <v>6.9065000000000001E-2</v>
+      </c>
+      <c r="H79" s="7">
+        <f t="shared" si="17"/>
+        <v>4.479543900984667E-3</v>
+      </c>
+      <c r="I79" s="5">
+        <v>0.34982600000000003</v>
+      </c>
+      <c r="J79" s="7">
+        <f t="shared" si="18"/>
+        <v>5.0218629157833226E-3</v>
+      </c>
+      <c r="K79" s="7">
+        <v>5.6777000000000001E-2</v>
+      </c>
+      <c r="L79" s="7">
+        <f t="shared" si="19"/>
+        <v>2.171073534084056E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="4">
+        <f t="shared" si="15"/>
+        <v>77</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="5">
+        <v>0.33335300000000001</v>
+      </c>
+      <c r="F80" s="7">
+        <f t="shared" si="16"/>
+        <v>1.2015968669834141E-2</v>
+      </c>
+      <c r="G80" s="7">
+        <v>7.0584999999999995E-2</v>
+      </c>
+      <c r="H80" s="7">
+        <f t="shared" si="17"/>
+        <v>2.6586383931817798E-2</v>
+      </c>
+      <c r="I80" s="5">
+        <v>0.35160999999999998</v>
+      </c>
+      <c r="J80" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0147150925941827E-2</v>
+      </c>
+      <c r="K80" s="7">
+        <v>5.7834000000000003E-2</v>
+      </c>
+      <c r="L80" s="7">
+        <f t="shared" si="19"/>
+        <v>2.0828185123733547E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" s="4">
+        <f t="shared" si="15"/>
+        <v>78</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="5">
+        <v>0.33340999999999998</v>
+      </c>
+      <c r="F81" s="7">
+        <f t="shared" si="16"/>
+        <v>1.2189013190849864E-2</v>
+      </c>
+      <c r="G81" s="7">
+        <v>7.0357000000000003E-2</v>
+      </c>
+      <c r="H81" s="7">
+        <f t="shared" si="17"/>
+        <v>2.3270357927192929E-2</v>
+      </c>
+      <c r="I81" s="5">
+        <v>0.35152299999999997</v>
+      </c>
+      <c r="J81" s="7">
+        <f t="shared" si="18"/>
+        <v>9.8972069478679373E-3</v>
+      </c>
+      <c r="K81" s="7">
+        <v>5.7592999999999998E-2</v>
+      </c>
+      <c r="L81" s="7">
+        <f t="shared" si="19"/>
+        <v>1.6574293077276016E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="4">
+        <f t="shared" si="15"/>
+        <v>79</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="5">
+        <v>0.33157700000000001</v>
+      </c>
+      <c r="F82" s="7">
+        <f t="shared" si="16"/>
+        <v>6.6242656992365314E-3</v>
+      </c>
+      <c r="G82" s="7">
+        <v>6.9478999999999999E-2</v>
+      </c>
+      <c r="H82" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0500749014645788E-2</v>
+      </c>
+      <c r="I82" s="5">
+        <v>0.34988900000000001</v>
+      </c>
+      <c r="J82" s="7">
+        <f t="shared" si="18"/>
+        <v>5.2028568309402121E-3</v>
+      </c>
+      <c r="K82" s="7">
+        <v>5.6981999999999998E-2</v>
+      </c>
+      <c r="L82" s="7">
+        <f t="shared" si="19"/>
+        <v>5.7895294242241487E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="4">
+        <f t="shared" si="15"/>
+        <v>80</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" s="5">
+        <v>0.33357199999999998</v>
+      </c>
+      <c r="F83" s="7">
+        <f t="shared" si="16"/>
+        <v>1.2680823934789497E-2</v>
+      </c>
+      <c r="G83" s="7">
+        <v>7.0202000000000001E-2</v>
+      </c>
+      <c r="H83" s="7">
+        <f t="shared" si="17"/>
+        <v>2.1016042002996085E-2</v>
+      </c>
+      <c r="I83" s="5">
+        <v>0.35145199999999999</v>
+      </c>
+      <c r="J83" s="7">
+        <f t="shared" si="18"/>
+        <v>9.6932296784053816E-3</v>
+      </c>
+      <c r="K83" s="7">
+        <v>5.6855000000000003E-2</v>
+      </c>
+      <c r="L83" s="7">
+        <f t="shared" si="19"/>
+        <v>3.5478518727715567E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="4">
+        <f t="shared" si="15"/>
+        <v>81</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="5">
+        <v>0.33186700000000002</v>
+      </c>
+      <c r="F84" s="7">
+        <f t="shared" si="16"/>
+        <v>7.5046676482643324E-3</v>
+      </c>
+      <c r="G84" s="7">
+        <v>6.9531999999999997E-2</v>
+      </c>
+      <c r="H84" s="7">
+        <f t="shared" si="17"/>
+        <v>1.1271579620984015E-2</v>
+      </c>
+      <c r="I84" s="5">
+        <v>0.35049799999999998</v>
+      </c>
+      <c r="J84" s="7">
+        <f t="shared" si="18"/>
+        <v>6.9524646774572875E-3</v>
+      </c>
+      <c r="K84" s="7">
+        <v>5.7014000000000002E-2</v>
+      </c>
+      <c r="L84" s="7">
+        <f t="shared" si="19"/>
+        <v>6.3543615631729304E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" s="4">
+        <f t="shared" si="15"/>
+        <v>82</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="5">
+        <v>0.33349000000000001</v>
+      </c>
+      <c r="F85" s="7">
+        <f t="shared" si="16"/>
+        <v>1.2431882694030011E-2</v>
+      </c>
+      <c r="G85" s="7">
+        <v>7.0152999999999993E-2</v>
+      </c>
+      <c r="H85" s="7">
+        <f t="shared" si="17"/>
+        <v>2.0303387291475697E-2</v>
+      </c>
+      <c r="I85" s="5">
+        <v>0.35144500000000001</v>
+      </c>
+      <c r="J85" s="7">
+        <f t="shared" si="18"/>
+        <v>9.6731192433880016E-3</v>
+      </c>
+      <c r="K85" s="7">
+        <v>5.6682999999999997E-2</v>
+      </c>
+      <c r="L85" s="7">
+        <f t="shared" si="19"/>
+        <v>5.1187912592216443E-4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" s="4">
+        <f t="shared" si="15"/>
+        <v>83</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="5">
+        <v>0.331397</v>
+      </c>
+      <c r="F86" s="7">
+        <f t="shared" si="16"/>
+        <v>6.0778093170813273E-3</v>
+      </c>
+      <c r="G86" s="7">
+        <v>6.9286E-2</v>
+      </c>
+      <c r="H86" s="7">
+        <f t="shared" si="17"/>
+        <v>7.6937620896781666E-3</v>
+      </c>
+      <c r="I86" s="5">
+        <v>0.34974699999999997</v>
+      </c>
+      <c r="J86" s="7">
+        <f t="shared" si="18"/>
+        <v>4.7949022920149393E-3</v>
+      </c>
+      <c r="K86" s="7">
+        <v>5.6876000000000003E-2</v>
+      </c>
+      <c r="L86" s="7">
+        <f t="shared" si="19"/>
+        <v>3.9185229639566487E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" s="4">
+        <f t="shared" si="15"/>
+        <v>84</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="5">
+        <v>0.33358300000000002</v>
+      </c>
+      <c r="F87" s="7">
+        <f t="shared" si="16"/>
+        <v>1.2714218491476874E-2</v>
+      </c>
+      <c r="G87" s="7">
+        <v>7.0249000000000006E-2</v>
+      </c>
+      <c r="H87" s="7">
+        <f t="shared" si="17"/>
+        <v>2.1699608767107453E-2</v>
+      </c>
+      <c r="I87" s="5">
+        <v>0.35131000000000001</v>
+      </c>
+      <c r="J87" s="7">
+        <f t="shared" si="18"/>
+        <v>9.2852751394802684E-3</v>
+      </c>
+      <c r="K87" s="7">
+        <v>5.6835999999999998E-2</v>
+      </c>
+      <c r="L87" s="7">
+        <f t="shared" si="19"/>
+        <v>3.2124827902706723E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" s="4">
+        <f t="shared" si="15"/>
+        <v>85</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="5">
+        <v>0.33078299999999999</v>
+      </c>
+      <c r="F88" s="7">
+        <f t="shared" si="16"/>
+        <v>4.2137858801742601E-3</v>
+      </c>
+      <c r="G88" s="7">
+        <v>6.9114999999999996E-2</v>
+      </c>
+      <c r="H88" s="7">
+        <f t="shared" si="17"/>
+        <v>5.2067425862093635E-3</v>
+      </c>
+      <c r="I88" s="5">
+        <v>0.34937299999999999</v>
+      </c>
+      <c r="J88" s="7">
+        <f t="shared" si="18"/>
+        <v>3.7204304782261178E-3</v>
+      </c>
+      <c r="K88" s="7">
+        <v>5.6675000000000003E-2</v>
+      </c>
+      <c r="L88" s="7">
+        <f t="shared" si="19"/>
+        <v>3.7067109118509169E-4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="4">
+        <f t="shared" si="15"/>
+        <v>86</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" s="5">
+        <v>0.333592</v>
+      </c>
+      <c r="F89" s="7">
+        <f t="shared" si="16"/>
+        <v>1.2741541310584576E-2</v>
+      </c>
+      <c r="G89" s="7">
+        <v>7.0435999999999999E-2</v>
+      </c>
+      <c r="H89" s="7">
+        <f t="shared" si="17"/>
+        <v>2.4419331849848014E-2</v>
+      </c>
+      <c r="I89" s="5">
+        <v>0.35144799999999998</v>
+      </c>
+      <c r="J89" s="7">
+        <f t="shared" si="18"/>
+        <v>9.6817380012525472E-3</v>
+      </c>
+      <c r="K89" s="7">
+        <v>5.6981999999999998E-2</v>
+      </c>
+      <c r="L89" s="7">
+        <f t="shared" si="19"/>
+        <v>5.7895294242241487E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" s="4">
+        <f t="shared" si="15"/>
+        <v>87</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="5">
+        <v>0.33052999999999999</v>
+      </c>
+      <c r="F90" s="7">
+        <f t="shared" si="16"/>
+        <v>3.4457110763672708E-3</v>
+      </c>
+      <c r="G90" s="7">
+        <v>6.8981000000000001E-2</v>
+      </c>
+      <c r="H90" s="7">
+        <f t="shared" si="17"/>
+        <v>3.2578501098070303E-3</v>
+      </c>
+      <c r="I90" s="5">
+        <v>0.34896300000000002</v>
+      </c>
+      <c r="J90" s="7">
+        <f t="shared" si="18"/>
+        <v>2.5425335700619534E-3</v>
+      </c>
+      <c r="K90" s="7">
+        <v>5.6535000000000002E-2</v>
+      </c>
+      <c r="L90" s="7">
+        <f t="shared" si="19"/>
+        <v>-2.1004695167155195E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" s="4">
+        <f t="shared" si="15"/>
+        <v>88</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E91" s="5">
+        <v>0.33335100000000001</v>
+      </c>
+      <c r="F91" s="7">
+        <f t="shared" si="16"/>
+        <v>1.2009896932254634E-2</v>
+      </c>
+      <c r="G91" s="7">
+        <v>7.0388999999999993E-2</v>
+      </c>
+      <c r="H91" s="7">
+        <f t="shared" si="17"/>
+        <v>2.3735765085736646E-2</v>
+      </c>
+      <c r="I91" s="5">
+        <v>0.35108800000000001</v>
+      </c>
+      <c r="J91" s="7">
+        <f t="shared" si="18"/>
+        <v>8.6474870574986436E-3</v>
+      </c>
+      <c r="K91" s="7">
+        <v>5.6721000000000001E-2</v>
+      </c>
+      <c r="L91" s="7">
+        <f t="shared" si="19"/>
+        <v>1.1826172909238115E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" s="4">
+        <f t="shared" si="15"/>
+        <v>89</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="5">
+        <v>0.32994000000000001</v>
+      </c>
+      <c r="F92" s="7">
+        <f t="shared" si="16"/>
+        <v>1.654548490414298E-3</v>
+      </c>
+      <c r="G92" s="7">
+        <v>6.8805000000000005E-2</v>
+      </c>
+      <c r="H92" s="7">
+        <f t="shared" si="17"/>
+        <v>6.9811073781587865E-4</v>
+      </c>
+      <c r="I92" s="5">
+        <v>0.34843600000000002</v>
+      </c>
+      <c r="J92" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0285051051776468E-3</v>
+      </c>
+      <c r="K92" s="7">
+        <v>5.6369000000000002E-2</v>
+      </c>
+      <c r="L92" s="7">
+        <f t="shared" si="19"/>
+        <v>-5.0305362375119237E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" s="4">
+        <f t="shared" si="15"/>
+        <v>90</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" s="5">
+        <v>0.33321400000000001</v>
+      </c>
+      <c r="F93" s="7">
+        <f t="shared" si="16"/>
+        <v>1.1593982908058765E-2</v>
+      </c>
+      <c r="G93" s="7">
+        <v>7.0690000000000003E-2</v>
+      </c>
+      <c r="H93" s="7">
+        <f t="shared" si="17"/>
+        <v>2.8113501170789944E-2</v>
+      </c>
+      <c r="I93" s="5">
+        <v>0.35087299999999999</v>
+      </c>
+      <c r="J93" s="7">
+        <f t="shared" si="18"/>
+        <v>8.029809410534397E-3</v>
+      </c>
+      <c r="K93" s="7">
+        <v>5.7026E-2</v>
+      </c>
+      <c r="L93" s="7">
+        <f t="shared" si="19"/>
+        <v>6.566173615278662E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" s="4">
+        <f t="shared" si="15"/>
+        <v>91</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="5">
+        <v>0.32993800000000001</v>
+      </c>
+      <c r="F94" s="7">
+        <f t="shared" si="16"/>
+        <v>1.6484767528347902E-3</v>
+      </c>
+      <c r="G94" s="7">
+        <v>6.8860000000000005E-2</v>
+      </c>
+      <c r="H94" s="7">
+        <f t="shared" si="17"/>
+        <v>1.4980292915631262E-3</v>
+      </c>
+      <c r="I94" s="5">
+        <v>0.34862599999999999</v>
+      </c>
+      <c r="J94" s="7">
+        <f t="shared" si="18"/>
+        <v>1.5743597699366032E-3</v>
+      </c>
+      <c r="K94" s="7">
+        <v>5.6619000000000003E-2</v>
+      </c>
+      <c r="L94" s="7">
+        <f t="shared" si="19"/>
+        <v>-6.1778515197515277E-4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" s="4">
+        <f t="shared" si="15"/>
+        <v>92</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E95" s="5">
+        <v>0.33343299999999998</v>
+      </c>
+      <c r="F95" s="7">
+        <f t="shared" si="16"/>
+        <v>1.225883817301412E-2</v>
+      </c>
+      <c r="G95" s="7">
+        <v>7.0971999999999993E-2</v>
+      </c>
+      <c r="H95" s="7">
+        <f t="shared" si="17"/>
+        <v>3.2214901755457548E-2</v>
+      </c>
+      <c r="I95" s="5">
+        <v>0.35107300000000002</v>
+      </c>
+      <c r="J95" s="7">
+        <f t="shared" si="18"/>
+        <v>8.6043932681755964E-3</v>
+      </c>
+      <c r="K95" s="7">
+        <v>5.7242000000000001E-2</v>
+      </c>
+      <c r="L95" s="7">
+        <f t="shared" si="19"/>
+        <v>1.0378790553182445E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" s="4">
+        <f t="shared" si="15"/>
+        <v>93</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E96" s="5">
+        <v>0.32960499999999998</v>
+      </c>
+      <c r="F96" s="7">
+        <f t="shared" si="16"/>
+        <v>6.3753244584765394E-4</v>
+      </c>
+      <c r="G96" s="7">
+        <v>6.8189E-2</v>
+      </c>
+      <c r="H96" s="7">
+        <f t="shared" si="17"/>
+        <v>-8.2609770641534543E-3</v>
+      </c>
+      <c r="I96" s="5">
+        <v>0.34789999999999999</v>
+      </c>
+      <c r="J96" s="7">
+        <f t="shared" si="18"/>
+        <v>-5.1137963330061503E-4</v>
+      </c>
+      <c r="K96" s="7">
+        <v>5.5474000000000002E-2</v>
+      </c>
+      <c r="L96" s="7">
+        <f t="shared" si="19"/>
+        <v>-2.0828185123733547E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" s="4">
+        <f t="shared" si="15"/>
+        <v>94</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E97" s="5">
+        <v>0.33004299999999998</v>
+      </c>
+      <c r="F97" s="7">
+        <f t="shared" si="16"/>
+        <v>1.9672429757585327E-3</v>
+      </c>
+      <c r="G97" s="7">
+        <v>6.7837999999999996E-2</v>
+      </c>
+      <c r="H97" s="7">
+        <f t="shared" si="17"/>
+        <v>-1.3365911834431449E-2</v>
+      </c>
+      <c r="I97" s="5">
+        <v>0.34820800000000002</v>
+      </c>
+      <c r="J97" s="7">
+        <f t="shared" si="18"/>
+        <v>3.734795074667718E-4</v>
+      </c>
+      <c r="K97" s="7">
+        <v>5.5098000000000001E-2</v>
+      </c>
+      <c r="L97" s="7">
+        <f t="shared" si="19"/>
+        <v>-2.746496275638087E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" s="4">
+        <f t="shared" si="15"/>
+        <v>95</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E98" s="5">
+        <v>0.32979000000000003</v>
+      </c>
+      <c r="F98" s="7">
+        <f t="shared" si="16"/>
+        <v>1.1991681719517122E-3</v>
+      </c>
+      <c r="G98" s="7">
+        <v>6.8183999999999995E-2</v>
+      </c>
+      <c r="H98" s="7">
+        <f t="shared" si="17"/>
+        <v>-8.3336969326760057E-3</v>
+      </c>
+      <c r="I98" s="5">
+        <v>0.34848299999999999</v>
+      </c>
+      <c r="J98" s="7">
+        <f t="shared" si="18"/>
+        <v>1.163532311723202E-3</v>
+      </c>
+      <c r="K98" s="7">
+        <v>5.5542000000000001E-2</v>
+      </c>
+      <c r="L98" s="7">
+        <f t="shared" si="19"/>
+        <v>-1.9627916828467571E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" s="4">
+        <f t="shared" si="15"/>
+        <v>96</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E99" s="5">
+        <v>0.33049800000000001</v>
+      </c>
+      <c r="F99" s="7">
+        <f t="shared" si="16"/>
+        <v>3.348563275095313E-3</v>
+      </c>
+      <c r="G99" s="7">
+        <v>6.7962999999999996E-2</v>
+      </c>
+      <c r="H99" s="7">
+        <f t="shared" si="17"/>
+        <v>-1.1547915121369505E-2</v>
+      </c>
+      <c r="I99" s="5">
+        <v>0.34910000000000002</v>
+      </c>
+      <c r="J99" s="7">
+        <f t="shared" si="18"/>
+        <v>2.9361235125461042E-3</v>
+      </c>
+      <c r="K99" s="7">
+        <v>5.5259000000000003E-2</v>
+      </c>
+      <c r="L99" s="7">
+        <f t="shared" si="19"/>
+        <v>-2.4623151057295165E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A101:L101"/>
     <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A100:L100"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:H1"/>
-    <mergeCell ref="A50:L50"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <conditionalFormatting sqref="E3:E33">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G33">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I33">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K33">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E49">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G49">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I49">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K49">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2705,7 +4992,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G33">
+  <conditionalFormatting sqref="G1:G1048576">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2717,7 +5004,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I33">
+  <conditionalFormatting sqref="I1:I1048576">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -2729,7 +5016,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K33">
+  <conditionalFormatting sqref="K1:K1048576">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2741,7 +5028,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E49">
+  <conditionalFormatting sqref="E3:E99">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2753,7 +5040,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G49">
+  <conditionalFormatting sqref="G3:G99">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2765,7 +5052,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I49">
+  <conditionalFormatting sqref="I3:I99">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2777,7 +5064,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K49">
+  <conditionalFormatting sqref="K3:K99">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2790,5 +5077,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>